--- a/01_analyses_states/Gujarat/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Gujarat/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>5.3</v>
+        <v>10.3</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>10.5</v>
+        <v>17.9</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>28.9</v>
+        <v>20.5</v>
       </c>
       <c r="E4">
-        <v>32.5</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>15.8</v>
+        <v>12.8</v>
       </c>
       <c r="E5">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="6">
@@ -475,10 +475,10 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
       <c r="E6">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C8">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3">
@@ -693,7 +693,7 @@
         <v>81</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>163</v>
       </c>
       <c r="C4">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Gujarat/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Gujarat/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>11.6</v>
+        <v>10.3</v>
       </c>
       <c r="E2">
-        <v>31.8</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>16.3</v>
+        <v>17.9</v>
       </c>
       <c r="E3">
-        <v>22.4</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>23.3</v>
+        <v>20.5</v>
       </c>
       <c r="E4">
-        <v>30.6</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="5">
@@ -453,13 +453,13 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="E5">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>37.2</v>
+        <v>38.5</v>
       </c>
       <c r="E6">
-        <v>11.8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="7">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>78</v>
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C8">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3">
@@ -693,7 +693,7 @@
         <v>81</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">

--- a/01_analyses_states/Gujarat/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Gujarat/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>21</v>
-      </c>
       <c r="D2">
-        <v>10.3</v>
+        <v>41.7</v>
       </c>
       <c r="E2">
-        <v>24.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>17.9</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>27.1</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>20.5</v>
+        <v>3.3</v>
       </c>
       <c r="E4">
-        <v>34.1</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>12.8</v>
+        <v>3.3</v>
       </c>
       <c r="E5">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>38.5</v>
+        <v>26.7</v>
       </c>
       <c r="E6">
-        <v>9.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C8">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C4">
-        <v>85</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C2">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="D2">
         <v>66</v>
       </c>
-      <c r="D2">
-        <v>68</v>
-      </c>
       <c r="E2">
-        <v>89.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="3">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4">
-        <v>26.2</v>
+        <v>28.2</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
     </row>
   </sheetData>
